--- a/Resources/quotation-template.xlsx
+++ b/Resources/quotation-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\重构 work（服务器版本）\backend\quotation\quotation-template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\QUO\Quotix\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA656974-0D42-4A20-9413-5F35B34A2F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C06CDA-5EBB-4388-8A7C-F8A974A6096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{30453385-D3B6-4967-9350-161A33167876}"/>
+    <workbookView xWindow="250" yWindow="530" windowWidth="22640" windowHeight="13600" xr2:uid="{30453385-D3B6-4967-9350-161A33167876}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -395,6 +395,36 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -405,9 +435,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -425,33 +452,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,7 +472,7 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
@@ -487,61 +487,37 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1026" name="Picture 1">
+        <xdr:cNvPr id="3" name="图片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4794929-1AFA-08DB-6A8E-07FA9B176204}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D591C1D-5591-BB24-EF02-DDEF3CE0043A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="1441450" cy="501650"/>
+          <a:ext cx="1441824" cy="508000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -824,12 +800,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19"/>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="20"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -837,41 +813,41 @@
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:12" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="2"/>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
     </row>
     <row r="4" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4"/>
@@ -884,119 +860,119 @@
       <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="25"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="34"/>
     </row>
     <row r="8" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="I8" s="12"/>
       <c r="K8" s="17"/>
     </row>
     <row r="9" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="I9" s="12"/>
       <c r="J9" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="27"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="36"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
       <c r="G11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
       <c r="G12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
       <c r="G13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
     </row>
     <row r="15" spans="1:12" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12"/>
@@ -1019,64 +995,64 @@
       <c r="B16" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30" t="s">
+      <c r="D16" s="19"/>
+      <c r="E16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
       <c r="H16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="I16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30" t="s">
+      <c r="J16" s="19"/>
+      <c r="K16" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="L16" s="30"/>
+      <c r="L16" s="19"/>
     </row>
     <row r="17" spans="1:12" ht="35.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>1</v>
       </c>
       <c r="B17" s="9"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35">
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18">
         <f>SUM(I17*H17)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="35"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="1:12" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="36">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22">
         <f>SUM(K17:L17)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="37"/>
+      <c r="L18" s="23"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
@@ -1230,6 +1206,19 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="A4:D5"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="A7:E9"/>
+    <mergeCell ref="H11:L11"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="H2:L3"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:G16"/>
@@ -1243,19 +1232,6 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="H2:L3"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="A4:D5"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A7:E9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
